--- a/九龙-启德-The Henley II/The Henley II_销控明细表.xlsx
+++ b/九龙-启德-The Henley II/The Henley II_销控明细表.xlsx
@@ -912,7 +912,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -974,7 +974,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2022-11-07</t>
+          <t>2022-11-08</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2023-06-22</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2023-11-30</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
+          <t>2022-09-05</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
+          <t>2022-08-03</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2023-02-20</t>
+          <t>2023-02-21</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2022-08-04</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2023-12-29</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
+          <t>2022-08-12</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-26</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2022-09-05</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
@@ -12166,14 +12166,14 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
         <v>14613200</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>30700</v>
+        <v>30508</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>14613200</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>30700</v>
+        <v>30508</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2023-01-25</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2022-08-28</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2022-09-12</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14664,7 +14664,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2022-11-06</t>
+          <t>2022-11-07</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2022-07-29</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15238,7 +15238,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15990,7 +15990,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16246,7 +16246,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16308,7 +16308,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16432,7 +16432,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16556,7 +16556,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16618,7 +16618,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17184,7 +17184,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17518,7 +17518,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17580,7 +17580,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17642,7 +17642,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17704,7 +17704,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17828,7 +17828,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2022-10-19</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -18170,7 +18170,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18356,7 +18356,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2023-01-08</t>
+          <t>2023-01-09</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18760,7 +18760,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18884,7 +18884,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18946,7 +18946,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19412,7 +19412,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19536,7 +19536,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2023-02-16</t>
+          <t>2023-02-17</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19881,7 +19881,7 @@
           <t>E | 573呎 (2房)
 $2108万
 $36,789/呎
-(22年-11月-07日)</t>
+(22年-11月-08日)</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
@@ -19889,7 +19889,7 @@
           <t>F | 381呎 (1房)
 $859万
 $22,546/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
@@ -19897,7 +19897,7 @@
           <t>G | 380呎 (1房)
 $858万
 $22,589/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -19928,7 +19928,7 @@
           <t>A | 888呎 (3房)
 $3163万
 $35,618/呎
-(25年-04月-01日)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -19936,7 +19936,7 @@
           <t>B | 550呎 (2房)
 $1908万
 $34,700/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -19944,7 +19944,7 @@
           <t>C | 543呎 (2房)
 $1908万
 $35,135/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -19952,7 +19952,7 @@
           <t>D | 479呎 (2房)
 $1533万
 $31,998/呎
-(25年-05月-27日)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -19960,7 +19960,7 @@
           <t>E | 573呎 (2房)
 $1569万
 $27,381/呎
-(23年-06月-22日)</t>
+(23年-06月-23日)</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
@@ -19968,7 +19968,7 @@
           <t>F | 381呎 (1房)
 $835万
 $21,919/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -19976,7 +19976,7 @@
           <t>G | 380呎 (1房)
 $835万
 $21,962/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -19984,7 +19984,7 @@
           <t>H | 379呎 (1房)
 $834万
 $22,009/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
@@ -19992,7 +19992,7 @@
           <t>J | 414呎 (1房)
 $919万
 $22,191/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
           <t>A | 888呎 (3房)
 $3450万
 $38,851/呎
-(22年-05月-23日)</t>
+(22年-05月-24日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -20015,7 +20015,7 @@
           <t>B | 550呎 (2房)
 $1886万
 $34,300/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -20023,7 +20023,7 @@
           <t>C | 543呎 (2房)
 $1886万
 $34,736/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -20031,7 +20031,7 @@
           <t>D | 479呎 (2房)
 $1523万
 $31,800/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -20039,7 +20039,7 @@
           <t>E | 575呎 (2房)
 $1548万
 $26,915/呎
-(22年-05月-17日)</t>
+(22年-05月-18日)</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -20047,7 +20047,7 @@
           <t>F | 381呎 (1房)
 $755万
 $19,806/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
@@ -20055,7 +20055,7 @@
           <t>G | 380呎 (1房)
 $825万
 $21,718/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
@@ -20063,7 +20063,7 @@
           <t>H | 379呎 (1房)
 $825万
 $21,762/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
@@ -20071,7 +20071,7 @@
           <t>J | 414呎 (1房)
 $898万
 $21,691/呎
-(25年-08月-07日)</t>
+(25年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
           <t>A | 888呎 (3房)
 $3313万
 $37,309/呎
-(23年-11月-30日)</t>
+(23年-12月-01日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -20094,7 +20094,7 @@
           <t>B | 550呎 (2房)
 $1876万
 $34,100/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -20102,7 +20102,7 @@
           <t>C | 543呎 (2房)
 $1873万
 $34,490/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -20110,7 +20110,7 @@
           <t>D | 479呎 (2房)
 $1553万
 $32,412/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -20118,7 +20118,7 @@
           <t>E | 575呎 (2房)
 $1523万
 $26,483/呎
-(22年-07月-21日)</t>
+(22年-07月-22日)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -20126,7 +20126,7 @@
           <t>F | 381呎 (1房)
 $750万
 $19,696/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -20134,7 +20134,7 @@
           <t>G | 380呎 (1房)
 $821万
 $21,596/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -20142,7 +20142,7 @@
           <t>H | 379呎 (1房)
 $820万
 $21,639/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
@@ -20150,7 +20150,7 @@
           <t>J | 414呎 (1房)
 $903万
 $21,808/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
     </row>
@@ -20165,7 +20165,7 @@
           <t>A | 888呎 (3房)
 $3081万
 $34,700/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -20173,7 +20173,7 @@
           <t>B | 550呎 (2房)
 $1870万
 $34,000/呎
-(26年-01月-22日)</t>
+(26年-01月-23日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -20181,7 +20181,7 @@
           <t>C | 543呎 (2房)
 $1866万
 $34,359/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -20189,7 +20189,7 @@
           <t>D | 479呎 (2房)
 $1506万
 $31,435/呎
-(25年-02月-05日)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -20197,7 +20197,7 @@
           <t>E | 573呎 (2房)
 $1518万
 $26,499/呎
-(22年-07月-24日)</t>
+(22年-07月-25日)</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
@@ -20205,7 +20205,7 @@
           <t>F | 381呎 (1房)
 $748万
 $19,638/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
@@ -20213,7 +20213,7 @@
           <t>G | 380呎 (1房)
 $818万
 $21,534/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -20221,7 +20221,7 @@
           <t>H | 379呎 (1房)
 $818万
 $21,579/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
@@ -20229,7 +20229,7 @@
           <t>J | 414呎 (1房)
 $880万
 $21,260/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -20244,7 +20244,7 @@
           <t>A | 888呎 (3房)
 $3072万
 $34,600/呎
-(25年-03月-06日)</t>
+(25年-03月-07日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -20252,7 +20252,7 @@
           <t>B | 550呎 (2房)
 $1864万
 $33,900/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -20260,7 +20260,7 @@
           <t>C | 543呎 (2房)
 $1958万
 $36,063/呎
-(22年-10月-26日)</t>
+(22年-10月-27日)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -20268,7 +20268,7 @@
           <t>D | 479呎 (2房)
 $1580万
 $32,996/呎
-(22年-09月-04日)</t>
+(22年-09月-05日)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -20276,7 +20276,7 @@
           <t>E | 573呎 (2房)
 $1546万
 $26,980/呎
-(22年-07月-27日)</t>
+(22年-07月-28日)</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
@@ -20284,7 +20284,7 @@
           <t>F | 381呎 (1房)
 $746万
 $19,583/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -20292,7 +20292,7 @@
           <t>G | 380呎 (1房)
 $738万
 $19,418/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
@@ -20300,7 +20300,7 @@
           <t>H | 379呎 (1房)
 $745万
 $19,661/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
@@ -20308,7 +20308,7 @@
           <t>J | 414呎 (1房)
 $878万
 $21,196/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -20323,7 +20323,7 @@
           <t>A | 888呎 (3房)
 $3260万
 $36,712/呎
-(22年-05月-17日)</t>
+(22年-05月-18日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -20331,7 +20331,7 @@
           <t>B | 550呎 (2房)
 $1859万
 $33,800/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -20339,7 +20339,7 @@
           <t>C | 542呎 (2房)
 $1855万
 $34,225/呎
-(22年-12月-18日)</t>
+(22年-12月-19日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -20347,7 +20347,7 @@
           <t>D | 479呎 (2房)
 $1497万
 $31,255/呎
-(23年-01月-09日)</t>
+(23年-01月-10日)</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -20355,7 +20355,7 @@
           <t>E | 573呎 (2房)
 $1557万
 $27,180/呎
-(22年-07月-31日)</t>
+(22年-08月-01日)</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -20363,7 +20363,7 @@
           <t>F | 381呎 (1房)
 $744万
 $19,525/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
@@ -20371,7 +20371,7 @@
           <t>G | 380呎 (1房)
 $736万
 $19,361/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="I11" s="23" t="inlineStr">
@@ -20379,7 +20379,7 @@
           <t>H | 379呎 (1房)
 $743万
 $19,606/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -20387,7 +20387,7 @@
           <t>J | 414呎 (1房)
 $875万
 $21,135/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -20402,7 +20402,7 @@
           <t>A | 888呎 (3房)
 $3215万
 $36,200/呎
-(24年-04月-28日)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -20410,7 +20410,7 @@
           <t>B | 550呎 (2房)
 $1854万
 $33,700/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -20418,7 +20418,7 @@
           <t>C | 543呎 (2房)
 $1850万
 $34,062/呎
-(23年-04月-19日)</t>
+(23年-04月-20日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -20426,7 +20426,7 @@
           <t>D | 479呎 (2房)
 $1493万
 $31,163/呎
-(23年-03月-20日)</t>
+(23年-03月-21日)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -20434,7 +20434,7 @@
           <t>E | 573呎 (2房)
 $1553万
 $27,101/呎
-(22年-08月-02日)</t>
+(22年-08月-03日)</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
@@ -20442,7 +20442,7 @@
           <t>F | 381呎 (1房)
 $742万
 $19,473/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
@@ -20450,7 +20450,7 @@
           <t>G | 380呎 (1房)
 $734万
 $19,305/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
@@ -20458,7 +20458,7 @@
           <t>H | 379呎 (1房)
 $898万
 $23,697/呎
-(24年-11月-28日)</t>
+(24年-11月-29日)</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
@@ -20466,7 +20466,7 @@
           <t>J | 414呎 (1房)
 $872万
 $21,074/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -20481,7 +20481,7 @@
           <t>A | 888呎 (3房)
 $3189万
 $35,910/呎
-(23年-05月-15日)</t>
+(23年-05月-16日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -20489,7 +20489,7 @@
           <t>B | 550呎 (2房)
 $1848万
 $33,600/呎
-(25年-02月-27日)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -20497,7 +20497,7 @@
           <t>C | 543呎 (2房)
 $1844万
 $33,962/呎
-(23年-06月-28日)</t>
+(23年-06月-29日)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -20505,7 +20505,7 @@
           <t>D | 479呎 (2房)
 $1488万
 $31,074/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -20513,7 +20513,7 @@
           <t>E | 573呎 (2房)
 $1383万
 $24,133/呎
-(25年-04月-22日)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -20521,7 +20521,7 @@
           <t>F | 381呎 (1房)
 $809万
 $21,246/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
@@ -20529,7 +20529,7 @@
           <t>G | 380呎 (1房)
 $732万
 $19,252/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -20537,7 +20537,7 @@
           <t>H | 379呎 (1房)
 $739万
 $19,492/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="J13" s="23" t="inlineStr">
@@ -20545,7 +20545,7 @@
           <t>J | 414呎 (1房)
 $870万
 $21,013/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -20560,7 +20560,7 @@
           <t>A | 888呎 (3房)
 $3179万
 $35,800/呎
-(22年-06月-08日)</t>
+(22年-06月-09日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -20568,7 +20568,7 @@
           <t>B | 550呎 (2房)
 $1842万
 $33,500/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -20576,7 +20576,7 @@
           <t>C | 543呎 (2房)
 $1839万
 $33,862/呎
-(23年-08月-28日)</t>
+(23年-08月-29日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -20584,7 +20584,7 @@
           <t>D | 479呎 (2房)
 $1547万
 $32,287/呎
-(24年-04月-09日)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
@@ -20592,7 +20592,7 @@
           <t>E | 575呎 (2房)
 $1497万
 $26,030/呎
-(22年-08月-10日)</t>
+(22年-08月-11日)</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
@@ -20600,7 +20600,7 @@
           <t>F | 381呎 (1房)
 $807万
 $21,186/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -20608,7 +20608,7 @@
           <t>G | 380呎 (1房)
 $884万
 $23,268/呎
-(24年-12月-04日)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
@@ -20616,7 +20616,7 @@
           <t>H | 379呎 (1房)
 $893万
 $23,560/呎
-(24年-12月-01日)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
@@ -20624,7 +20624,7 @@
           <t>J | 414呎 (1房)
 $867万
 $20,949/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -20639,7 +20639,7 @@
           <t>A | 888呎 (3房)
 $3030万
 $34,122/呎
-(24年-12月-19日)</t>
+(24年-12月-20日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -20647,7 +20647,7 @@
           <t>B | 550呎 (2房)
 $1837万
 $33,400/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -20655,7 +20655,7 @@
           <t>C | 543呎 (2房)
 $1833万
 $33,763/呎
-(25年-02月-09日)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -20663,7 +20663,7 @@
           <t>D | 479呎 (2房)
 $1480万
 $30,892/呎
-(25年-01月-19日)</t>
+(25年-01月-20日)</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -20671,7 +20671,7 @@
           <t>E | 573呎 (2房)
 $1492万
 $26,045/呎
-(22年-08月-08日)</t>
+(22年-08月-09日)</t>
         </is>
       </c>
       <c r="G15" s="23" t="inlineStr">
@@ -20679,7 +20679,7 @@
           <t>F | 381呎 (1房)
 $805万
 $21,126/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
@@ -20687,7 +20687,7 @@
           <t>G | 380呎 (1房)
 $727万
 $19,142/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="I15" s="23" t="inlineStr">
@@ -20695,7 +20695,7 @@
           <t>H | 379呎 (1房)
 $967万
 $25,504/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="J15" s="23" t="inlineStr">
@@ -20703,7 +20703,7 @@
           <t>J | 414呎 (1房)
 $865万
 $20,886/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -20718,7 +20718,7 @@
           <t>A | 888呎 (3房)
 $3010万
 $33,896/呎
-(23年-10月-19日)</t>
+(23年-10月-20日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -20726,7 +20726,7 @@
           <t>B | 550呎 (2房)
 $1832万
 $33,300/呎
-(26年-01月-28日)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -20734,7 +20734,7 @@
           <t>C | 543呎 (2房)
 $1905万
 $35,080/呎
-(22年-09月-15日)</t>
+(22年-09月-16日)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -20742,7 +20742,7 @@
           <t>D | 476呎 (2房)
 $1475万
 $30,995/呎
-(23年-02月-20日)</t>
+(23年-02月-21日)</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -20750,7 +20750,7 @@
           <t>E | 573呎 (2房)
 $1519万
 $26,515/呎
-(22年-08月-14日)</t>
+(22年-08月-15日)</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
@@ -20758,7 +20758,7 @@
           <t>F | 381呎 (1房)
 $726万
 $19,050/呎
-(25年-06月-11日)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
@@ -20766,7 +20766,7 @@
           <t>G | 380呎 (1房)
 $889万
 $23,399/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
@@ -20774,7 +20774,7 @@
           <t>H | 379呎 (1房)
 $964万
 $25,432/呎
-(22年-05月-16日)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
@@ -20782,7 +20782,7 @@
           <t>J | 414呎 (1房)
 $862万
 $20,827/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -20797,7 +20797,7 @@
           <t>A | 888呎 (3房)
 $2948万
 $33,200/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -20805,7 +20805,7 @@
           <t>B | 550呎 (2房)
 $1820万
 $33,100/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -20813,7 +20813,7 @@
           <t>C | 543呎 (2房)
 $1817万
 $33,463/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -20821,7 +20821,7 @@
           <t>D | 479呎 (2房)
 $1467万
 $30,620/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -20829,7 +20829,7 @@
           <t>E | 573呎 (2房)
 $1557万
 $27,176/呎
-(22年-08月-14日)</t>
+(22年-08月-15日)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -20837,7 +20837,7 @@
           <t>F | 381呎 (1房)
 $722万
 $18,938/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -20845,7 +20845,7 @@
           <t>G | 380呎 (1房)
 $797万
 $20,982/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
@@ -20853,7 +20853,7 @@
           <t>H | 379呎 (1房)
 $728万
 $19,213/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="J17" s="23" t="inlineStr">
@@ -20861,7 +20861,7 @@
           <t>J | 414呎 (1房)
 $775万
 $18,719/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -20876,7 +20876,7 @@
           <t>A | 888呎 (3房)
 $3019万
 $34,000/呎
-(22年-05月-17日)</t>
+(22年-05月-18日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -20884,7 +20884,7 @@
           <t>B | 550呎 (2房)
 $1815万
 $33,000/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -20892,7 +20892,7 @@
           <t>C | 543呎 (2房)
 $1812万
 $33,364/呎
-(25年-05月-20日)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -20900,7 +20900,7 @@
           <t>D | 479呎 (2房)
 $1462万
 $30,529/呎
-(23年-08月-13日)</t>
+(23年-08月-14日)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -20908,7 +20908,7 @@
           <t>E | 573呎 (2房)
 $1553万
 $27,096/呎
-(22年-08月-07日)</t>
+(22年-08月-08日)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -20916,7 +20916,7 @@
           <t>F | 381呎 (1房)
 $719万
 $18,882/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -20924,7 +20924,7 @@
           <t>G | 380呎 (1房)
 $795万
 $20,922/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
@@ -20932,7 +20932,7 @@
           <t>H | 379呎 (1房)
 $880万
 $23,218/呎
-(25年-05月-26日)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
@@ -20940,7 +20940,7 @@
           <t>J | 414呎 (1房)
 $773万
 $18,664/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -20955,7 +20955,7 @@
           <t>A | 888呎 (3房)
 $2984万
 $33,600/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -20963,7 +20963,7 @@
           <t>B | 550呎 (2房)
 $1810万
 $32,900/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -20971,7 +20971,7 @@
           <t>C | 543呎 (2房)
 $1806万
 $33,266/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -20979,7 +20979,7 @@
           <t>D | 479呎 (2房)
 $1458万
 $30,440/呎
-(23年-02月-09日)</t>
+(23年-02月-10日)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -20987,7 +20987,7 @@
           <t>E | 575呎 (2房)
 $1471万
 $25,578/呎
-(22年-07月-31日)</t>
+(22年-08月-01日)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -20995,7 +20995,7 @@
           <t>F | 381呎 (1房)
 $717万
 $18,827/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
@@ -21003,7 +21003,7 @@
           <t>G | 380呎 (1房)
 $793万
 $20,859/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="I19" s="23" t="inlineStr">
@@ -21011,7 +21011,7 @@
           <t>H | 379呎 (1房)
 $724万
 $19,100/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="J19" s="23" t="inlineStr">
@@ -21019,7 +21019,7 @@
           <t>J | 414呎 (1房)
 $770万
 $18,607/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
           <t>A | 888呎 (3房)
 $3010万
 $33,900/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -21042,7 +21042,7 @@
           <t>B | 550呎 (2房)
 $1804万
 $32,800/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -21050,7 +21050,7 @@
           <t>C | 543呎 (2房)
 $1801万
 $33,166/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -21058,7 +21058,7 @@
           <t>D | 479呎 (2房)
 $1515万
 $31,626/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -21066,7 +21066,7 @@
           <t>E | 573呎 (2房)
 $1497万
 $26,125/呎
-(22年-08月-04日)</t>
+(22年-08月-05日)</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -21074,7 +21074,7 @@
           <t>F | 381呎 (1房)
 $715万
 $18,772/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -21082,7 +21082,7 @@
           <t>G | 380呎 (1房)
 $790万
 $20,797/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
@@ -21090,7 +21090,7 @@
           <t>H | 379呎 (1房)
 $885万
 $23,346/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
@@ -21098,7 +21098,7 @@
           <t>J | 414呎 (1房)
 $768万
 $18,552/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -21113,7 +21113,7 @@
           <t>A | 888呎 (3房)
 $3038万
 $34,212/呎
-(22年-05月-17日)</t>
+(22年-05月-18日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -21121,7 +21121,7 @@
           <t>B | 550呎 (2房)
 $1798万
 $32,691/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -21129,7 +21129,7 @@
           <t>C | 543呎 (2房)
 $1796万
 $33,066/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -21137,7 +21137,7 @@
           <t>D | 479呎 (2房)
 $1465万
 $30,576/呎
-(23年-12月-28日)</t>
+(23年-12月-29日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -21145,7 +21145,7 @@
           <t>E | 575呎 (2房)
 $1447万
 $25,163/呎
-(22年-07月-31日)</t>
+(22年-08月-01日)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -21153,7 +21153,7 @@
           <t>F | 381呎 (1房)
 $713万
 $18,717/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
@@ -21161,7 +21161,7 @@
           <t>G | 380呎 (1房)
 $788万
 $20,740/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -21169,7 +21169,7 @@
           <t>H | 379呎 (1房)
 $732万
 $19,312/呎
-(25年-06月-18日)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
@@ -21177,7 +21177,7 @@
           <t>J | 414呎 (1房)
 $779万
 $18,814/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
     </row>
@@ -21192,7 +21192,7 @@
           <t>A | 888呎 (3房)
 $3110万
 $35,023/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -21200,7 +21200,7 @@
           <t>B | 550呎 (2房)
 $1886万
 $34,300/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -21216,7 +21216,7 @@
           <t>D | 479呎 (2房)
 $1447万
 $30,210/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -21224,7 +21224,7 @@
           <t>E | 575呎 (2房)
 $1443万
 $25,088/呎
-(22年-08月-07日)</t>
+(22年-08月-08日)</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
@@ -21232,7 +21232,7 @@
           <t>F | 381呎 (1房)
 $711万
 $18,662/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
@@ -21240,7 +21240,7 @@
           <t>G | 380呎 (1房)
 $786万
 $20,675/呎
-(25年-08月-07日)</t>
+(25年-08月-08日)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -21248,7 +21248,7 @@
           <t>H | 379呎 (1房)
 $895万
 $23,604/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
@@ -21256,7 +21256,7 @@
           <t>J | 414呎 (1房)
 $763万
 $18,438/呎
-(25年-06月-10日)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -21271,7 +21271,7 @@
           <t>A | 888呎 (3房)
 $2940万
 $33,108/呎
-(25年-08月-05日)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -21279,7 +21279,7 @@
           <t>B | 550呎 (2房)
 $1741万
 $31,655/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -21287,7 +21287,7 @@
           <t>C | 543呎 (2房)
 $1742万
 $32,081/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -21295,7 +21295,7 @@
           <t>D | 479呎 (2房)
 $1443万
 $30,121/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
@@ -21303,7 +21303,7 @@
           <t>E | 575呎 (2房)
 $1453万
 $25,275/呎
-(22年-07月-26日)</t>
+(22年-07月-27日)</t>
         </is>
       </c>
       <c r="G23" s="23" t="inlineStr">
@@ -21311,7 +21311,7 @@
           <t>F | 381呎 (1房)
 $933万
 $24,486/呎
-(23年-05月-02日)</t>
+(23年-05月-03日)</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
@@ -21319,7 +21319,7 @@
           <t>G | 380呎 (1房)
 $932万
 $24,532/呎
-(23年-02月-01日)</t>
+(23年-02月-02日)</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
@@ -21327,7 +21327,7 @@
           <t>H | 379呎 (1房)
 $951万
 $25,102/呎
-(22年-06月-16日)</t>
+(22年-06月-17日)</t>
         </is>
       </c>
       <c r="J23" s="23" t="inlineStr">
@@ -21335,7 +21335,7 @@
           <t>J | 414呎 (1房)
 $842万
 $20,330/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -21350,7 +21350,7 @@
           <t>A | 888呎 (3房)
 $2939万
 $33,100/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -21366,7 +21366,7 @@
           <t>C | 543呎 (2房)
 $1808万
 $33,297/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -21374,7 +21374,7 @@
           <t>D | 479呎 (2房)
 $1438万
 $30,011/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -21382,7 +21382,7 @@
           <t>E | 573呎 (2房)
 $1479万
 $25,819/呎
-(22年-08月-22日)</t>
+(22年-08月-23日)</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
@@ -21390,7 +21390,7 @@
           <t>F | 381呎 (1房)
 $960万
 $25,184/呎
-(22年-07月-25日)</t>
+(22年-07月-26日)</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
@@ -21398,7 +21398,7 @@
           <t>G | 380呎 (1房)
 $949万
 $24,975/呎
-(22年-08月-11日)</t>
+(22年-08月-12日)</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -21406,7 +21406,7 @@
           <t>H | 379呎 (1房)
 $949万
 $25,028/呎
-(22年-05月-17日)</t>
+(22年-05月-18日)</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
@@ -21414,7 +21414,7 @@
           <t>J | 414呎 (1房)
 $839万
 $20,266/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
     </row>
@@ -21429,7 +21429,7 @@
           <t>A | 888呎 (3房)
 $2930万
 $33,000/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -21450,10 +21450,10 @@
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>D | 476呎 (2房)
+          <t>D | 479呎 (2房)
 $1461万
-$30,700/呎
-(26年-07月-13日)</t>
+$30,508/呎
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -21461,7 +21461,7 @@
           <t>E | 573呎 (2房)
 $1328万
 $23,176/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -21469,7 +21469,7 @@
           <t>F | 381呎 (1房)
 $715万
 $18,764/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
@@ -21477,7 +21477,7 @@
           <t>G | 380呎 (1房)
 $969万
 $25,490/呎
-(22年-09月-05日)</t>
+(22年-09月-06日)</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -21485,7 +21485,7 @@
           <t>H | 379呎 (1房)
 $939万
 $24,768/呎
-(22年-06月-08日)</t>
+(22年-06月-09日)</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
@@ -21493,7 +21493,7 @@
           <t>J | 414呎 (1房)
 $839万
 $20,266/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -21508,7 +21508,7 @@
           <t>A | 888呎 (3房)
 $2930万
 $32,995/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -21540,7 +21540,7 @@
           <t>E | 573呎 (2房)
 $1505万
 $26,272/呎
-(22年-08月-24日)</t>
+(22年-08月-25日)</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
@@ -21548,7 +21548,7 @@
           <t>F | 381呎 (1房)
 $705万
 $18,497/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
@@ -21556,7 +21556,7 @@
           <t>G | 380呎 (1房)
 $936万
 $24,644/呎
-(23年-01月-25日)</t>
+(23年-01月-26日)</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
@@ -21564,7 +21564,7 @@
           <t>H | 379呎 (1房)
 $936万
 $24,692/呎
-(22年-05月-17日)</t>
+(22年-05月-18日)</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -21572,7 +21572,7 @@
           <t>J | 414呎 (1房)
 $836万
 $20,205/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -21587,7 +21587,7 @@
           <t>A | 888呎 (3房)
 $2920万
 $32,883/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -21603,7 +21603,7 @@
           <t>C | 543呎 (2房)
 $1772万
 $32,640/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -21619,7 +21619,7 @@
           <t>E | 573呎 (2房)
 $1440万
 $25,136/呎
-(22年-08月-28日)</t>
+(22年-08月-29日)</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
@@ -21627,7 +21627,7 @@
           <t>F | 381呎 (1房)
 $703万
 $18,441/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H27" s="23" t="inlineStr">
@@ -21635,7 +21635,7 @@
           <t>G | 380呎 (1房)
 $924万
 $24,315/呎
-(23年-04月-19日)</t>
+(23年-04月-20日)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -21643,7 +21643,7 @@
           <t>H | 379呎 (1房)
 $933万
 $24,605/呎
-(22年-05月-18日)</t>
+(22年-05月-19日)</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -21651,7 +21651,7 @@
           <t>J | 414呎 (1房)
 $914万
 $22,080/呎
-(25年-04月-21日)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -21666,7 +21666,7 @@
           <t>A | 888呎 (3房)
 $2913万
 $32,800/呎
-(26年-01月-28日)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -21674,7 +21674,7 @@
           <t>B | 550呎 (2房)
 $1766万
 $32,100/呎
-(26年-01月-28日)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -21682,7 +21682,7 @@
           <t>C | 543呎 (2房)
 $1767万
 $32,540/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -21698,7 +21698,7 @@
           <t>E | 573呎 (2房)
 $1436万
 $25,060/呎
-(22年-09月-12日)</t>
+(22年-09月-13日)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -21706,7 +21706,7 @@
           <t>F | 381呎 (1房)
 $701万
 $18,386/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
@@ -21714,7 +21714,7 @@
           <t>G | 380呎 (1房)
 $700万
 $18,421/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
@@ -21722,7 +21722,7 @@
           <t>H | 379呎 (1房)
 $931万
 $24,560/呎
-(22年-05月-25日)</t>
+(22年-05月-26日)</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
@@ -21730,7 +21730,7 @@
           <t>J | 414呎 (1房)
 $911万
 $22,012/呎
-(24年-05月-09日)</t>
+(24年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -21745,7 +21745,7 @@
           <t>A | 888呎 (3房)
 $2904万
 $32,700/呎
-(25年-08月-06日)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -21761,7 +21761,7 @@
           <t>C | 543呎 (2房)
 $1789万
 $32,939/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -21777,7 +21777,7 @@
           <t>E | 573呎 (2房)
 $1497万
 $26,134/呎
-(22年-10月-26日)</t>
+(22年-10月-27日)</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -21785,7 +21785,7 @@
           <t>F | 381呎 (1房)
 $739万
 $19,392/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
@@ -21793,7 +21793,7 @@
           <t>G | 380呎 (1房)
 $738万
 $19,429/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -21801,7 +21801,7 @@
           <t>H | 379呎 (1房)
 $745万
 $19,661/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
@@ -21809,7 +21809,7 @@
           <t>J | 414呎 (1房)
 $794万
 $19,167/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
     </row>
@@ -21824,7 +21824,7 @@
           <t>A | 888呎 (3房)
 $2859万
 $32,200/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -21832,7 +21832,7 @@
           <t>B | 550呎 (2房)
 $1760万
 $32,000/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -21856,7 +21856,7 @@
           <t>E | 575呎 (2房)
 $1423万
 $24,748/呎
-(22年-05月-16日)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -21864,7 +21864,7 @@
           <t>F | 381呎 (1房)
 $914万
 $23,977/呎
-(22年-07月-28日)</t>
+(22年-07月-29日)</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
@@ -21872,7 +21872,7 @@
           <t>G | 380呎 (1房)
 $694万
 $18,253/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
@@ -21880,7 +21880,7 @@
           <t>H | 379呎 (1房)
 $922万
 $24,324/呎
-(22年-11月-06日)</t>
+(22年-11月-07日)</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
@@ -21888,7 +21888,7 @@
           <t>J | 414呎 (1房)
 $745万
 $17,990/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -21903,7 +21903,7 @@
           <t>A | 888呎 (3房)
 $2895万
 $32,600/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -21911,7 +21911,7 @@
           <t>B | 550呎 (2房)
 $1678万
 $30,509/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -21919,7 +21919,7 @@
           <t>C | 543呎 (2房)
 $1729万
 $31,841/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -21935,7 +21935,7 @@
           <t>E | 573呎 (2房)
 $1463万
 $25,531/呎
-(22年-09月-14日)</t>
+(22年-09月-15日)</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
@@ -21943,7 +21943,7 @@
           <t>F | 381呎 (1房)
 $911万
 $23,904/呎
-(22年-10月-10日)</t>
+(22年-10月-11日)</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
@@ -21951,7 +21951,7 @@
           <t>G | 380呎 (1房)
 $692万
 $18,200/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
@@ -21959,7 +21959,7 @@
           <t>H | 379呎 (1房)
 $919万
 $24,249/呎
-(23年-01月-31日)</t>
+(23年-02月-01日)</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">
@@ -21967,7 +21967,7 @@
           <t>J | 414呎 (1房)
 $900万
 $21,740/呎
-(24年-04月-14日)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -21982,7 +21982,7 @@
           <t>A | 888呎 (3房)
 $2895万
 $32,600/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -21990,7 +21990,7 @@
           <t>B | 550呎 (2房)
 $1754万
 $31,900/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -21998,7 +21998,7 @@
           <t>C | 543呎 (2房)
 $1756万
 $32,340/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -22014,7 +22014,7 @@
           <t>E | 573呎 (2房)
 $1463万
 $25,531/呎
-(22年-09月-21日)</t>
+(22年-09月-22日)</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
@@ -22022,7 +22022,7 @@
           <t>F | 381呎 (1房)
 $692万
 $18,164/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
@@ -22030,7 +22030,7 @@
           <t>G | 380呎 (1房)
 $692万
 $18,200/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
@@ -22038,7 +22038,7 @@
           <t>H | 379呎 (1房)
 $698万
 $18,426/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
@@ -22046,7 +22046,7 @@
           <t>J | 414呎 (1房)
 $743万
 $17,935/呎
-(25年-06月-11日)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -22061,7 +22061,7 @@
           <t>A | 888呎 (3房)
 $2843万
 $32,012/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
@@ -22069,7 +22069,7 @@
           <t>B | 550呎 (2房)
 $1704万
 $30,982/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -22077,7 +22077,7 @@
           <t>C | 543呎 (2房)
 $1704万
 $31,381/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -22093,7 +22093,7 @@
           <t>E | 573呎 (2房)
 $1400万
 $24,433/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
@@ -22101,7 +22101,7 @@
           <t>F | 381呎 (1房)
 $690万
 $18,108/呎
-(25年-06月-18日)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="H33" s="23" t="inlineStr">
@@ -22109,7 +22109,7 @@
           <t>G | 380呎 (1房)
 $690万
 $18,145/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
@@ -22117,7 +22117,7 @@
           <t>H | 379呎 (1房)
 $696万
 $18,370/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
@@ -22125,7 +22125,7 @@
           <t>J | 414呎 (1房)
 $740万
 $17,880/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -22140,7 +22140,7 @@
           <t>A | 888呎 (3房)
 $2877万
 $32,400/呎
-(26年-06月-25日)</t>
+(26年-07月-27日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -22172,7 +22172,7 @@
           <t>E | 573呎 (2房)
 $1445万
 $25,218/呎
-(22年-09月-28日)</t>
+(22年-09月-29日)</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
@@ -22180,7 +22180,7 @@
           <t>F | 381呎 (1房)
 $704万
 $18,487/呎
-(25年-07月-08日)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="H34" s="23" t="inlineStr">
@@ -22188,7 +22188,7 @@
           <t>G | 380呎 (1房)
 $732万
 $19,263/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">
@@ -22196,7 +22196,7 @@
           <t>H | 379呎 (1房)
 $841万
 $22,198/呎
-(24年-08月-29日)</t>
+(24年-08月-30日)</t>
         </is>
       </c>
       <c r="J34" s="23" t="inlineStr">
@@ -22204,7 +22204,7 @@
           <t>J | 414呎 (1房)
 $895万
 $21,607/呎
-(24年-08月-29日)</t>
+(24年-08月-30日)</t>
         </is>
       </c>
     </row>
@@ -22251,7 +22251,7 @@
           <t>E | 573呎 (2房)
 $1432万
 $24,985/呎
-(22年-10月-19日)</t>
+(22年-10月-20日)</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
@@ -22259,7 +22259,7 @@
           <t>F | 381呎 (1房)
 $698万
 $18,318/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="H35" s="23" t="inlineStr">
@@ -22267,7 +22267,7 @@
           <t>G | 380呎 (1房)
 $697万
 $18,352/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
@@ -22275,7 +22275,7 @@
           <t>H | 379呎 (1房)
 $713万
 $18,811/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="J35" s="23" t="inlineStr">
@@ -22283,7 +22283,7 @@
           <t>J | 414呎 (1房)
 $813万
 $19,647/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
           <t>E | 573呎 (2房)
 $1369万
 $23,899/呎
-(23年-01月-08日)</t>
+(23年-01月-09日)</t>
         </is>
       </c>
       <c r="G36" s="23" t="inlineStr">
@@ -22338,7 +22338,7 @@
           <t>F | 381呎 (1房)
 $696万
 $18,260/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="H36" s="23" t="inlineStr">
@@ -22346,7 +22346,7 @@
           <t>G | 380呎 (1房)
 $897万
 $23,613/呎
-(22年-05月-17日)</t>
+(22年-05月-18日)</t>
         </is>
       </c>
       <c r="I36" s="23" t="inlineStr">
@@ -22354,7 +22354,7 @@
           <t>H | 379呎 (1房)
 $711万
 $18,754/呎
-(25年-06月-06日)</t>
+(25年-06月-07日)</t>
         </is>
       </c>
       <c r="J36" s="23" t="inlineStr">
@@ -22362,7 +22362,7 @@
           <t>J | 414呎 (1房)
 $811万
 $19,586/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
           <t>E | 573呎 (2房)
 $1390万
 $24,250/呎
-(22年-08月-16日)</t>
+(22年-08月-17日)</t>
         </is>
       </c>
       <c r="G37" s="23" t="inlineStr">
@@ -22417,7 +22417,7 @@
           <t>F | 381呎 (1房)
 $691万
 $18,148/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="H37" s="23" t="inlineStr">
@@ -22425,7 +22425,7 @@
           <t>G | 380呎 (1房)
 $920万
 $24,200/呎
-(22年-08月-21日)</t>
+(22年-08月-22日)</t>
         </is>
       </c>
       <c r="I37" s="23" t="inlineStr">
@@ -22433,7 +22433,7 @@
           <t>H | 379呎 (1房)
 $706万
 $18,638/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="J37" s="23" t="inlineStr">
@@ -22441,7 +22441,7 @@
           <t>J | 414呎 (1房)
 $806万
 $19,461/呎
-(25年-08月-21日)</t>
+(25年-08月-22日)</t>
         </is>
       </c>
     </row>
@@ -22467,7 +22467,7 @@
           <t>E | 573呎 (2房)
 $1376万
 $24,020/呎
-(23年-02月-16日)</t>
+(23年-02月-17日)</t>
         </is>
       </c>
       <c r="G38" s="23" t="inlineStr">
@@ -22475,7 +22475,7 @@
           <t>F | 381呎 (1房)
 $685万
 $17,969/呎
-(25年-07月-15日)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="H38" s="23" t="inlineStr">
@@ -22483,7 +22483,7 @@
           <t>G | 380呎 (1房)
 $684万
 $18,002/呎
-(25年-07月-17日)</t>
+(25年-07月-18日)</t>
         </is>
       </c>
       <c r="I38" s="23" t="inlineStr">
@@ -22491,7 +22491,7 @@
           <t>H | 379呎 (1房)
 $702万
 $18,523/呎
-(25年-07月-16日)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="J38" s="23" t="inlineStr">
@@ -22499,7 +22499,7 @@
           <t>J | 414呎 (1房)
 $801万
 $19,336/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-The Henley II/The Henley II_销控明细表.xlsx
+++ b/九龙-启德-The Henley II/The Henley II_销控明细表.xlsx
@@ -11662,7 +11662,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -21366,7 +21366,7 @@
           <t>C | 543呎 (2房)
 $1808万
 $33,297/呎
-(26年-07月-03日)</t>
+(26年-08月-03日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">

--- a/九龙-启德-The Henley II/The Henley II_销控明细表.xlsx
+++ b/九龙-启德-The Henley II/The Henley II_销控明细表.xlsx
@@ -12166,7 +12166,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -21453,7 +21453,7 @@
           <t>D | 479呎 (2房)
 $1461万
 $30,508/呎
-(26年-07月-14日)</t>
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -22061,7 +22061,7 @@
           <t>A | 888呎 (3房)
 $2843万
 $32,012/呎
-(26年-07月-22日)</t>
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">

--- a/九龙-启德-The Henley II/The Henley II_销控明细表.xlsx
+++ b/九龙-启德-The Henley II/The Henley II_销控明细表.xlsx
@@ -15176,7 +15176,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -21832,7 +21832,7 @@
           <t>B | 550呎 (2房)
 $1760万
 $32,000/呎
-(26年-07月-20日)</t>
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
